--- a/LD-05A_报表与仪表板规格册.xlsx
+++ b/LD-05A_报表与仪表板规格册.xlsx
@@ -2935,7 +2935,7 @@
       </c>
       <c r="S27" s="27" t="inlineStr">
         <is>
-          <t>—（坐席状态时长改以平台历史指标为唯一来源，DD-65；报表须标注来源且不可下钻）</t>
+          <t>—（坐席状态时长以平台历史指标为唯一来源，DD-65；报表须标注来源，不可下钻，且不可按班次切分——同表中的在岗时长可以，须在版式上区分）</t>
         </is>
       </c>
       <c r="T27" s="28" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="S28" s="28" t="inlineStr">
         <is>
-          <t>在岗区间由 fact_agent_state 推算，非排班计划（DD-53）</t>
+          <t>在岗区间由 fact_agent_session 的签入签出推算，非排班计划（DD-53）</t>
         </is>
       </c>
       <c r="T28" s="28" t="inlineStr">
